--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/RHODE_ISLAND_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/RHODE_ISLAND_2011.xlsx
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C60">
